--- a/backend/sample_data/service_catalog.xlsx
+++ b/backend/sample_data/service_catalog.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Общий анализ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ мочи</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Биохимия</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Биохимия</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Биохимия</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Биохимия</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Общий анализ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -597,7 +597,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Гормоны</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Гормоны</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Биохимия</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Биохимия</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -677,7 +677,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Биохимия</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ кала</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Биохимия</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Инфекции</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Инфекции</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Биохимия</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -797,7 +797,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Биохимия</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Биохимия</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Биохимия</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Гормоны</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Гормоны</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -895,7 +895,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ крови &gt; Общий анализ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -913,7 +913,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>лаборатория</t>
+          <t>Лаборатория &gt; Анализ мочи</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -931,7 +931,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>диагностика</t>
+          <t>Диагностика &gt; УЗИ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>диагностика</t>
+          <t>Диагностика &gt; УЗИ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>диагностика</t>
+          <t>Диагностика &gt; УЗИ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>диагностика</t>
+          <t>Диагностика &gt; УЗИ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>диагностика</t>
+          <t>Диагностика &gt; УЗИ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>диагностика</t>
+          <t>Диагностика &gt; Рентген</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>диагностика</t>
+          <t>Диагностика &gt; Рентген</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>диагностика</t>
+          <t>Диагностика &gt; КТ и МРТ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>диагностика</t>
+          <t>Диагностика &gt; КТ и МРТ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>диагностика</t>
+          <t>Диагностика &gt; Эндоскопия</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>диагностика</t>
+          <t>Диагностика &gt; Эндоскопия</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>диагностика</t>
+          <t>Диагностика &gt; Рентген</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>консультация</t>
+          <t>Консультация</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>консультация</t>
+          <t>Консультация</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>консультация</t>
+          <t>Консультация</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>консультация</t>
+          <t>Консультация</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>консультация</t>
+          <t>Консультация</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>консультация</t>
+          <t>Консультация</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>консультация</t>
+          <t>Консультация</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>консультация</t>
+          <t>Консультация</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>консультация</t>
+          <t>Консультация</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>консультация</t>
+          <t>Консультация</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>консультация</t>
+          <t>Консультация</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>консультация</t>
+          <t>Консультация</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>процедура</t>
+          <t>Процедура</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>процедура</t>
+          <t>Процедура</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>процедура</t>
+          <t>Процедура</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>процедура</t>
+          <t>Процедура</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>процедура</t>
+          <t>Процедура</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>процедура</t>
+          <t>Процедура</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>процедура</t>
+          <t>Процедура</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>процедура</t>
+          <t>Процедура</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>стоматология</t>
+          <t>Стоматология</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>стоматология</t>
+          <t>Стоматология</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>стоматология</t>
+          <t>Стоматология</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>стоматология</t>
+          <t>Стоматология</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>стоматология</t>
+          <t>Стоматология</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>стоматология</t>
+          <t>Стоматология</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>стоматология</t>
+          <t>Стоматология</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>функциональная диагностика</t>
+          <t>Функциональная диагностика</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>функциональная диагностика</t>
+          <t>Функциональная диагностика</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>функциональная диагностика</t>
+          <t>Функциональная диагностика</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>функциональная диагностика</t>
+          <t>Функциональная диагностика</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>функциональная диагностика</t>
+          <t>Функциональная диагностика</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>функциональная диагностика</t>
+          <t>Функциональная диагностика</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>функциональная диагностика</t>
+          <t>Функциональная диагностика</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>физиотерапия</t>
+          <t>Физиотерапия</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>физиотерапия</t>
+          <t>Физиотерапия</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>физиотерапия</t>
+          <t>Физиотерапия</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>физиотерапия</t>
+          <t>Физиотерапия</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>физиотерапия</t>
+          <t>Физиотерапия</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>физиотерапия</t>
+          <t>Физиотерапия</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>физиотерапия</t>
+          <t>Физиотерапия</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>физиотерапия</t>
+          <t>Физиотерапия</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
